--- a/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
+++ b/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
+++ b/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
+++ b/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>The position of the body when the observation was done, e.g. standing, sitting. To be used only when the body position in not precoordinated in the observation code.</t>
   </si>
   <si>
-    <t>Observation.extension:BodyPosition.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:BodyPosition.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -565,10 +569,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:BodyPosition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -780,10 +780,6 @@
   </si>
   <si>
     <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Observation.category:VSCat.extension</t>
@@ -3611,7 +3607,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3637,10 +3633,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3663,13 +3659,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3720,7 +3716,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3729,7 +3725,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3744,7 +3740,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3755,10 +3751,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3829,7 +3825,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3838,7 +3834,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3873,10 +3869,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3902,13 +3898,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3916,7 +3912,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -3958,7 +3954,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -3993,10 +3989,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4019,13 +4015,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4064,17 +4060,17 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4083,7 +4079,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4112,7 +4108,7 @@
         <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>178</v>
@@ -4137,13 +4133,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4192,7 +4188,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4201,7 +4197,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -4975,7 +4971,7 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>232</v>
@@ -5097,7 +5093,7 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>232</v>
@@ -5219,13 +5215,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5276,7 +5272,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5300,7 +5296,7 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5311,10 +5307,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5340,10 +5336,10 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>189</v>
@@ -5387,7 +5383,7 @@
         <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
@@ -5396,7 +5392,7 @@
         <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5420,7 +5416,7 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5431,10 +5427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5457,19 +5453,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5518,7 +5514,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5539,10 +5535,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5553,10 +5549,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5579,13 +5575,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5636,7 +5632,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5660,7 +5656,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5671,10 +5667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5700,10 +5696,10 @@
         <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>189</v>
@@ -5747,7 +5743,7 @@
         <v>141</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
@@ -5756,7 +5752,7 @@
         <v>142</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5780,7 +5776,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5791,10 +5787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5820,65 +5816,65 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5899,10 +5895,10 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5913,10 +5909,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5939,16 +5935,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5998,7 +5994,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6019,10 +6015,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6033,10 +6029,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6062,63 +6058,63 @@
         <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6139,10 +6135,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6153,10 +6149,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6179,17 +6175,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6238,7 +6234,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6259,10 +6255,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6273,10 +6269,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6299,19 +6295,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6360,7 +6356,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6381,10 +6377,10 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6395,10 +6391,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6421,19 +6417,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6482,7 +6478,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6503,10 +6499,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6517,14 +6513,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6543,19 +6539,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6565,7 +6561,7 @@
         <v>20</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>20</v>
@@ -6583,11 +6579,11 @@
         <v>179</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
       </c>
@@ -6604,7 +6600,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>93</v>
@@ -6619,30 +6615,30 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6665,19 +6661,19 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6726,7 +6722,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6741,19 +6737,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>20</v>
@@ -6761,10 +6757,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6787,16 +6783,16 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6846,7 +6842,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6867,13 +6863,13 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>20</v>
@@ -6881,14 +6877,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6907,19 +6903,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6968,7 +6964,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6983,19 +6979,19 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -7003,14 +6999,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7029,19 +7025,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7090,7 +7086,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7099,25 +7095,25 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AJ39" t="s" s="2">
+      <c r="AK39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -7125,10 +7121,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7151,16 +7147,16 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7210,7 +7206,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7231,13 +7227,13 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7245,10 +7241,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7271,17 +7267,17 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7330,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7345,19 +7341,19 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>20</v>
@@ -7365,10 +7361,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7391,19 +7387,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7452,7 +7448,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7461,7 +7457,7 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7470,27 +7466,27 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7513,19 +7509,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7553,37 +7549,37 @@
         <v>179</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
@@ -7598,7 +7594,7 @@
         <v>136</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7609,14 +7605,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7635,19 +7631,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7675,11 +7671,11 @@
         <v>179</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7696,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7714,27 +7710,27 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7757,19 +7753,19 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7818,7 +7814,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7839,10 +7835,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7853,10 +7849,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7879,16 +7875,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7917,11 +7913,11 @@
         <v>179</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>434</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7938,7 +7934,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7956,27 +7952,27 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7999,19 +7995,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8039,11 +8035,11 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
       </c>
@@ -8060,7 +8056,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8081,10 +8077,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8095,10 +8091,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8121,16 +8117,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8180,7 +8176,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8198,27 +8194,27 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8241,16 +8237,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8300,7 +8296,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8318,27 +8314,27 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8361,19 +8357,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8422,7 +8418,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8434,19 +8430,19 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8457,10 +8453,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8483,13 +8479,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8540,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8564,7 +8560,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8575,10 +8571,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8604,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>189</v>
@@ -8660,7 +8656,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8684,7 +8680,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8695,14 +8691,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8724,10 +8720,10 @@
         <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>189</v>
@@ -8782,7 +8778,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8817,10 +8813,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8843,13 +8839,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8900,7 +8896,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8909,7 +8905,7 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8921,10 +8917,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8935,10 +8931,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8961,13 +8957,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9018,7 +9014,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9027,7 +9023,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -9039,10 +9035,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -9053,10 +9049,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9079,19 +9075,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9119,11 +9115,11 @@
         <v>117</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
       </c>
@@ -9140,7 +9136,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9158,13 +9154,13 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9175,10 +9171,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9201,19 +9197,19 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9238,14 +9234,14 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
       </c>
@@ -9262,7 +9258,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9280,13 +9276,13 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AN57" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9297,10 +9293,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9323,17 +9319,17 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9382,7 +9378,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9406,7 +9402,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9417,10 +9413,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9443,13 +9439,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9500,7 +9496,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9521,10 +9517,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9535,10 +9531,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9561,16 +9557,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9620,7 +9616,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9641,10 +9637,10 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9655,10 +9651,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9681,16 +9677,16 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9740,7 +9736,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9761,10 +9757,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9775,10 +9771,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9801,19 +9797,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9850,7 +9846,7 @@
         <v>20</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
@@ -9860,7 +9856,7 @@
         <v>142</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9872,19 +9868,19 @@
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9895,10 +9891,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9921,13 +9917,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9978,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10002,7 +9998,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10013,10 +10009,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10042,10 +10038,10 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>189</v>
@@ -10098,7 +10094,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10122,7 +10118,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10133,14 +10129,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10162,10 +10158,10 @@
         <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>189</v>
@@ -10220,7 +10216,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10255,10 +10251,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10281,19 +10277,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10321,11 +10317,11 @@
         <v>179</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
       </c>
@@ -10342,7 +10338,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>93</v>
@@ -10360,16 +10356,16 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>20</v>
@@ -10377,10 +10373,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10403,19 +10399,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10443,37 +10439,37 @@
         <v>179</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z67" t="s" s="2">
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10482,27 +10478,27 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10525,19 +10521,19 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="O68" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10565,11 +10561,11 @@
         <v>179</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
       </c>
@@ -10586,7 +10582,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10595,7 +10591,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10610,7 +10606,7 @@
         <v>136</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10621,14 +10617,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10647,19 +10643,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10687,11 +10683,11 @@
         <v>179</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
       </c>
@@ -10708,7 +10704,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10726,27 +10722,27 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10772,16 +10768,16 @@
         <v>20</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="N70" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10830,7 +10826,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10851,10 +10847,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10865,13 +10861,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>20</v>
@@ -10893,19 +10889,19 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M71" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10954,7 +10950,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10966,19 +10962,19 @@
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AK71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10989,10 +10985,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11015,13 +11011,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11072,7 +11068,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11096,7 +11092,7 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -11107,10 +11103,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11136,10 +11132,10 @@
         <v>138</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>189</v>
@@ -11192,7 +11188,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11216,7 +11212,7 @@
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11227,14 +11223,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11256,10 +11252,10 @@
         <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>189</v>
@@ -11314,7 +11310,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11349,10 +11345,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11375,19 +11371,19 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11397,7 +11393,7 @@
         <v>20</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>20</v>
@@ -11415,11 +11411,11 @@
         <v>179</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
       </c>
@@ -11436,7 +11432,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>93</v>
@@ -11454,16 +11450,16 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>20</v>
@@ -11471,10 +11467,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11497,19 +11493,19 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="O76" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11537,26 +11533,26 @@
         <v>179</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11565,7 +11561,7 @@
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11574,30 +11570,30 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>20</v>
@@ -11619,19 +11615,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11659,37 +11655,37 @@
         <v>179</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z77" t="s" s="2">
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI77" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>105</v>
@@ -11698,27 +11694,27 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11741,13 +11737,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11798,7 +11794,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11822,7 +11818,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11833,10 +11829,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11862,10 +11858,10 @@
         <v>138</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>189</v>
@@ -11909,7 +11905,7 @@
         <v>141</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>20</v>
@@ -11918,7 +11914,7 @@
         <v>142</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11942,7 +11938,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11953,10 +11949,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11979,19 +11975,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -12040,7 +12036,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12061,10 +12057,10 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12075,10 +12071,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12104,20 +12100,20 @@
         <v>113</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q81" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="R81" t="s" s="2">
         <v>20</v>
@@ -12141,28 +12137,28 @@
         <v>224</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="Z81" t="s" s="2">
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12183,10 +12179,10 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12197,10 +12193,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12223,17 +12219,17 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12282,7 +12278,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12303,10 +12299,10 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12317,10 +12313,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12346,72 +12342,72 @@
         <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="S83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF83" t="s" s="2">
+      <c r="AG83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI83" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12423,10 +12419,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12437,10 +12433,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12466,65 +12462,65 @@
         <v>113</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12545,10 +12541,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12559,10 +12555,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12585,19 +12581,19 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N85" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12625,11 +12621,11 @@
         <v>179</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
       </c>
@@ -12646,7 +12642,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12655,7 +12651,7 @@
         <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>105</v>
@@ -12670,7 +12666,7 @@
         <v>136</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12681,14 +12677,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12707,19 +12703,19 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12747,11 +12743,11 @@
         <v>179</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
       </c>
@@ -12768,7 +12764,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12786,27 +12782,27 @@
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12832,16 +12828,16 @@
         <v>20</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="N87" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O87" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12890,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12911,10 +12907,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12925,13 +12921,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>20</v>
@@ -12953,19 +12949,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -13014,7 +13010,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13026,19 +13022,19 @@
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13049,10 +13045,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13075,13 +13071,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13132,7 +13128,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13156,7 +13152,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13167,10 +13163,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13196,10 +13192,10 @@
         <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>189</v>
@@ -13252,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13276,7 +13272,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13287,14 +13283,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13316,10 +13312,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>189</v>
@@ -13374,7 +13370,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13409,10 +13405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13435,19 +13431,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13457,7 +13453,7 @@
         <v>20</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>20</v>
@@ -13475,11 +13471,11 @@
         <v>179</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
       </c>
@@ -13496,7 +13492,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>93</v>
@@ -13514,16 +13510,16 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>20</v>
@@ -13531,10 +13527,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13557,19 +13553,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13597,26 +13593,26 @@
         <v>179</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13625,7 +13621,7 @@
         <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13634,30 +13630,30 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>20</v>
@@ -13679,19 +13675,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13719,37 +13715,37 @@
         <v>179</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z94" t="s" s="2">
+      <c r="AA94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI94" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13758,27 +13754,27 @@
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13801,13 +13797,13 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13858,7 +13854,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13882,7 +13878,7 @@
         <v>20</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -13893,10 +13889,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13922,10 +13918,10 @@
         <v>138</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>189</v>
@@ -13969,7 +13965,7 @@
         <v>141</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>20</v>
@@ -13978,7 +13974,7 @@
         <v>142</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14002,7 +13998,7 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14013,10 +14009,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14039,19 +14035,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14100,7 +14096,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14121,10 +14117,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14135,10 +14131,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14164,20 +14160,20 @@
         <v>113</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q98" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>20</v>
@@ -14201,28 +14197,28 @@
         <v>224</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14243,10 +14239,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14257,10 +14253,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14283,17 +14279,17 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14342,7 +14338,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14363,10 +14359,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14377,10 +14373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14406,72 +14402,72 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>105</v>
@@ -14483,10 +14479,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14497,10 +14493,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14526,65 +14522,65 @@
         <v>113</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14605,10 +14601,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14619,10 +14615,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14645,19 +14641,19 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14685,11 +14681,11 @@
         <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
       </c>
@@ -14706,7 +14702,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14715,7 +14711,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14730,7 +14726,7 @@
         <v>136</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
@@ -14741,14 +14737,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14767,19 +14763,19 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14807,11 +14803,11 @@
         <v>179</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
       </c>
@@ -14828,7 +14824,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14846,27 +14842,27 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14892,16 +14888,16 @@
         <v>20</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14950,7 +14946,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14971,10 +14967,10 @@
         <v>20</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
+++ b/docs/StructureDefinition-twenty-four-hour-blood-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
